--- a/data/output/evaluasi_74.xlsx
+++ b/data/output/evaluasi_74.xlsx
@@ -8,9 +8,23 @@
   </bookViews>
   <sheets>
     <sheet name="7400" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="7472" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="7401" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="7413" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="7401" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="7403" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="7404" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="7405" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="7407" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="7408" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="7409" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="7411" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="7412" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="7414" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="7415" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="7471" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="7402" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="7413" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="7472" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="7406" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="7410" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,20 +488,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6.21225391867901</v>
+        <v>-8.220346336080846</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q1-25</t>
+          <t>adhb_pi_q3-25</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -506,16 +520,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5.101772111254032</v>
+        <v>6.351335026881823</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_net_ekspor_q1-25</t>
+          <t>adhb_net_ekspor_q1-25</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -534,16 +548,2474 @@
         </is>
       </c>
       <c r="D4" t="n">
+        <v>5.292641204093485</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>adhk_net_ekspor_q1-25</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>74</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sulawesi Tenggara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-5.825411134748324</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>adhk_net_ekspor_q3-25</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>74</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Sulawesi Tenggara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4.143766445250821</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25 vs q-to-q_pdrb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>74</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Sulawesi Tenggara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
         <v>2.113229798708126</v>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q1-25 vs q-to-q_pkrt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>74</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Sulawesi Tenggara</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2.400750307776792</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q1-25 vs q-to-q_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>74</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Sulawesi Tenggara</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.2296627951841473</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q2-25 vs q-to-q_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>74</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Sulawesi Tenggara</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-4.594693734244315</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25 vs q-to-q_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>74</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Sulawesi Tenggara</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>12.52019766476699</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q2-25 vs q-to-q_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>74</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Sulawesi Tenggara</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>5.993666358453023</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25 vs q-to-q_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>74</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Sulawesi Tenggara</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>16.46698117409466</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25 vs q-to-q_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>74</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Sulawesi Tenggara</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>5.677683624395692</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q3-25 vs y-on-y_pkrt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>74</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sulawesi Tenggara</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0.9173564535362271</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25 vs y-on-y_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>74</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulawesi Tenggara</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-1.485226231175554</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25 vs y-on-y_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>74</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Sulawesi Tenggara</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>5.051871438980101</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25 vs y-on-y_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>74</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Sulawesi Tenggara</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1.817388369520883</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q3-25 vs implisit_q-to-q_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7412</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe Kepulauan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-7.325579076896545</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7412</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe Kepulauan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>3.30295740289562</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7412</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe Kepulauan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-2.233338890059612</v>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>q-to-q_pkrt_q1-25 vs q-to-q_pkrt_q1-25.1</t>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7412</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe Kepulauan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2.489316873916603</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7412</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe Kepulauan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-2.837919619420616</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7412</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe Kepulauan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>13.77607416899107</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7412</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe Kepulauan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1.350127979546659</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7412</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe Kepulauan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.0463868574880812</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7412</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe Kepulauan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>6.479308078264881</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7412</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe Kepulauan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-8.206442412800939</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7412</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe Kepulauan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-2.522730906279376</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7412</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe Kepulauan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-2.29052845483955</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7414</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Tengah</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-2.625019197674292</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7414</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Tengah</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>3.392022570024176</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7414</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Tengah</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>5.008629375643829</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7414</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Tengah</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-3.521536875218346</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7414</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Tengah</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-12.55544600000037</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7414</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Tengah</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>21.69611300000008</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7414</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Tengah</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4.629344614247596</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7414</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Tengah</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>7.617477608942489</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7414</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Tengah</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.01666547561845854</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7415</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Selatan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-2.449367983549007</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7415</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Selatan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.153480898822505</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7415</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Selatan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-4.586006133157944</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7415</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Selatan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-4.60361613618845</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7415</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Selatan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-2.442698125430165</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7471</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Kendari</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-3.241898652598255</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7471</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Kendari</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>9.348532170050349</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7471</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Kendari</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>9.398582299886424</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q3-25_prov vs y-on-y_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7471</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Kendari</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6.393316334389458</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7471</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Kendari</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7.066327650256444</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7471</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Kendari</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2.32297749694766</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7402</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Muna</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2.733779017043903</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7402</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Muna</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-15.61250941501782</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7402</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Muna</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-9.724801933311157</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7402</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Muna</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-7.559707059266188</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7402</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Muna</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-19.32374966327536</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7402</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Muna</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>12.62142887107705</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7402</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Muna</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.3353172206945965</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7402</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Muna</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-6.829920727264242</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7413</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Muna Barat</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.204666891098931</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7413</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Muna Barat</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>9.408637589519305</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7413</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Muna Barat</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-4.138164413043741</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7413</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Muna Barat</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-6.496930044153336</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7413</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Muna Barat</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>11.10603582640066</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7413</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Muna Barat</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>8.384326359013228</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7472</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Baubau</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.2856002301845669</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7472</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Baubau</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>10.1116000000002</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7472</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Baubau</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-7.751383964293238</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7472</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Baubau</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-4.048514166925746</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7406</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Bombana</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-1.494104683575925</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7406</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Bombana</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>20.2982578419479</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7406</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Bombana</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-15.40795647416641</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7406</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Bombana</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-11.96593897990344</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7406</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Bombana</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.2496473065283089</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7410</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe Utara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>16.69902282687736</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7410</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe Utara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-2.412462184761143</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7410</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe Utara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.703436581497112</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7410</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe Utara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-2.455337278738805</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -558,7 +3030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -595,57 +3067,477 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7472</v>
+        <v>7401</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kota Baubau</t>
+          <t>Kabupaten Buton</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1.458919414381831</v>
+        <v>-27209.80831916607</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>q-to-q_pklnprt_q1-25_ril vs q-to-q_pklnprt_q1-25_rev</t>
+          <t>adhb_net_ekspor_q2-25_ril vs adhb_net_ekspor_q2-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7472</v>
+        <v>7401</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kota Baubau</t>
+          <t>Kabupaten Buton</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-13672.08407081501</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>adhk_net_ekspor_q2-25_ril vs adhk_net_ekspor_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7401</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>q1-25</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>0.01594200560312066</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>sog_q_pklnprt_q1-25_ril vs sog_q_pklnprt_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+      <c r="D4" t="n">
+        <v>14.7428906498085</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7401</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-16.73309769325672</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q2-25_ril vs y-on-y_pkp_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7401</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>14.7428906498085</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7401</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-4.728510220302227</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q2-25_ril vs c-to-c_pkp_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7401</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-9.226332667146238</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7401</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-9.607879391585588</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7401</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-1.187870566503432</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7401</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>12.74155516870198</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7401</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-5.344687603992885</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7401</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-30.58427012190016</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7401</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-4.04858384650848</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7401</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.9668762995358564</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7401</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-16.50619070316525</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7401</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-2.198138319449186</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7401</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-10.56588909141898</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -660,7 +3552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -697,11 +3589,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7401</v>
+        <v>7403</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Buton</t>
+          <t>Kabupaten Konawe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -710,72 +3602,212 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>9.762988113615284</v>
+        <v>-2.056695828087983</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7401</v>
+        <v>7403</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Buton</t>
+          <t>Kabupaten Konawe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>9.762988113615284</v>
+        <v>2.13454416092106</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7401</v>
+        <v>7403</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Buton</t>
+          <t>Kabupaten Konawe</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.066728554149545</v>
+        <v>9.279777806872101</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pkp_q1-25_ril vs sog_y-on-y_pkp_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7403</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>19.22529921140347</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7403</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>13.13030755715284</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7403</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.319419735941536</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7403</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>13.60029144560038</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7403</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Konawe</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.4938363481801461</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -790,6 +3822,360 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7404</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-2.709190160850787</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7404</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2.577416108638143</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7404</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.8700085419161409</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7404</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-9.844945718160632</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7404</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.506333162115465</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7404</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>21.02067214770529</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7404</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-4.098347248743308</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7404</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>15.13479803802077</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7404</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>7.379349673403786</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7404</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.5466717073366595</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7404</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>3.764683409020011</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -827,11 +4213,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7413</v>
+        <v>7405</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Muna Barat</t>
+          <t>Kabupaten Konawe Selatan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -840,72 +4226,1068 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2.069716653308928</v>
+        <v>-3.088563750001262</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7413</v>
+        <v>7405</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Muna Barat</t>
+          <t>Kabupaten Konawe Selatan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2.069716653308928</v>
+        <v>0.4586574114693915</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7413</v>
+        <v>7405</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Muna Barat</t>
+          <t>Kabupaten Konawe Selatan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.7366545812152347</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7407</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Wakatobi</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>q1-25</t>
         </is>
       </c>
+      <c r="D2" t="n">
+        <v>-2.607413689410151</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7407</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Wakatobi</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-2.331995417287963</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7407</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Wakatobi</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
       <c r="D4" t="n">
-        <v>0.3280183541696213</v>
+        <v>-0.01159047027141604</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pkp_q1-25_ril vs sog_y-on-y_pkp_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7407</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Wakatobi</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.586977862090924</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7407</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Wakatobi</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>25.83096907576503</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7407</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Wakatobi</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3.091603892519412</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7407</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Wakatobi</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2.614773625504969</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7407</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Wakatobi</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.5654779822219484</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7408</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka Utara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-3.554380578209887</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7408</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka Utara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.2499999999996341</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7408</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka Utara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.4499254488144316</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7408</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka Utara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-9.428822499903381</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7409</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Utara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-2.59354806434947</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7409</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Utara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2.018167902027401</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7409</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Utara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.1306968396513849</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7409</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Utara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.0947255879733697</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7409</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Utara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-5.324337106364891</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7409</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Utara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.04014769040121247</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7409</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Buton Utara</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1.873170621619258</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7411</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka Timur</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-2.718661260542144</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7411</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka Timur</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2.150601587455232</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7411</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka Timur</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.05698027886233538</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7411</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka Timur</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>11.84996693570816</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7411</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka Timur</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-2.777945910660125</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7411</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka Timur</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-6.890337675271081</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7411</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka Timur</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.08407429140993881</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7411</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka Timur</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-1.835537768594512</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7411</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka Timur</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-2.347586913682005</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7411</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Kolaka Timur</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-2.368881030766591</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>

--- a/data/output/evaluasi_74.xlsx
+++ b/data/output/evaluasi_74.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -641,7 +641,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -809,7 +809,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -837,7 +837,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
